--- a/training schedule_cv_part_not_updated.xlsx
+++ b/training schedule_cv_part_not_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guyle\Documents\Projects\CV_training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E02F95-4F58-477B-9B9C-06154483A278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7010512E-32B1-4432-8A54-EA6EA76E158E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -275,7 +275,7 @@
     <t>10.6-16.6</t>
   </si>
   <si>
-    <t>17.6-?</t>
+    <t>17.6-20.6</t>
   </si>
 </sst>
 </file>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C32" s="16">
         <f>SUM(C33,C40,C44)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" s="16"/>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C33" s="6">
         <f>SUM(C34:C39)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" s="6"/>
     </row>
@@ -1684,12 +1684,23 @@
       <c r="B36" s="4">
         <v>3</v>
       </c>
-      <c r="C36" s="4"/>
+      <c r="C36" s="4">
+        <v>2</v>
+      </c>
       <c r="D36" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>79</v>
+      </c>
+      <c r="F36" s="2">
+        <v>4</v>
+      </c>
+      <c r="G36" s="2">
+        <v>5</v>
+      </c>
+      <c r="H36" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">

--- a/training schedule_cv_part_not_updated.xlsx
+++ b/training schedule_cv_part_not_updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guyle\Documents\Projects\CV_training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7010512E-32B1-4432-8A54-EA6EA76E158E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4322C91D-8250-4CD5-9D5B-D818DD911C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
   <si>
     <t>Supervisor</t>
   </si>
@@ -276,6 +276,15 @@
   </si>
   <si>
     <t>17.6-20.6</t>
+  </si>
+  <si>
+    <t>some minor compatibility issues, I think second notebook (two stage detector) is redundant after first notebook (one stage detector)</t>
+  </si>
+  <si>
+    <t>22.6-26.6</t>
+  </si>
+  <si>
+    <t>26.6-?</t>
   </si>
 </sst>
 </file>
@@ -1621,7 +1630,7 @@
       </c>
       <c r="C32" s="16">
         <f>SUM(C33,C40,C44)</f>
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="D32" s="16"/>
     </row>
@@ -1635,7 +1644,7 @@
       </c>
       <c r="C33" s="6">
         <f>SUM(C34:C39)</f>
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="D33" s="6"/>
     </row>
@@ -1659,7 +1668,7 @@
         <v>2.5</v>
       </c>
       <c r="C35" s="4">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>21</v>
@@ -1685,7 +1694,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="4">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>22</v>
@@ -1710,9 +1719,26 @@
       <c r="B37" s="4">
         <v>5.5</v>
       </c>
-      <c r="C37" s="4"/>
+      <c r="C37" s="4">
+        <v>4.5</v>
+      </c>
       <c r="D37" s="4" t="s">
         <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="2">
+        <v>3</v>
+      </c>
+      <c r="G37" s="2">
+        <v>5</v>
+      </c>
+      <c r="H37" s="2">
+        <v>4</v>
+      </c>
+      <c r="I37" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -1737,6 +1763,9 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
         <v>6</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
